--- a/Teste de hipótese T/Salários Eng.xlsx
+++ b/Teste de hipótese T/Salários Eng.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abner\OneDrive\Documentos\Abner\Ciência de dados tópicos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abner\OneDrive\Documentos\Abner\Ciência de dados tópicos\Projetos\Projetos\Teste de hipótese T\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1D9F59-37F5-4663-B1D4-0266F3EC4E8B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59F88A9-A62F-4897-8E6D-D0E6F35B97AF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19485" yWindow="1650" windowWidth="15495" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
   <si>
     <t>Entrevistado</t>
   </si>
@@ -184,6 +184,156 @@
   </si>
   <si>
     <t>x51</t>
+  </si>
+  <si>
+    <t>6800.00</t>
+  </si>
+  <si>
+    <t>6800.01</t>
+  </si>
+  <si>
+    <t>6800.02</t>
+  </si>
+  <si>
+    <t>6800.03</t>
+  </si>
+  <si>
+    <t>6800.04</t>
+  </si>
+  <si>
+    <t>6800.05</t>
+  </si>
+  <si>
+    <t>6800.06</t>
+  </si>
+  <si>
+    <t>6800.07</t>
+  </si>
+  <si>
+    <t>6800.08</t>
+  </si>
+  <si>
+    <t>6800.09</t>
+  </si>
+  <si>
+    <t>6800.10</t>
+  </si>
+  <si>
+    <t>6800.11</t>
+  </si>
+  <si>
+    <t>6800.12</t>
+  </si>
+  <si>
+    <t>6800.13</t>
+  </si>
+  <si>
+    <t>6800.14</t>
+  </si>
+  <si>
+    <t>6800.15</t>
+  </si>
+  <si>
+    <t>6800.16</t>
+  </si>
+  <si>
+    <t>6800.17</t>
+  </si>
+  <si>
+    <t>7200.20</t>
+  </si>
+  <si>
+    <t>7200.21</t>
+  </si>
+  <si>
+    <t>7200.22</t>
+  </si>
+  <si>
+    <t>7200.23</t>
+  </si>
+  <si>
+    <t>7200.24</t>
+  </si>
+  <si>
+    <t>7200.25</t>
+  </si>
+  <si>
+    <t>6254.10</t>
+  </si>
+  <si>
+    <t>6254.11</t>
+  </si>
+  <si>
+    <t>6254.12</t>
+  </si>
+  <si>
+    <t>6254.13</t>
+  </si>
+  <si>
+    <t>6254.14</t>
+  </si>
+  <si>
+    <t>8011.15</t>
+  </si>
+  <si>
+    <t>8011.16</t>
+  </si>
+  <si>
+    <t>8011.17</t>
+  </si>
+  <si>
+    <t>8011.18</t>
+  </si>
+  <si>
+    <t>8011.19</t>
+  </si>
+  <si>
+    <t>8011.20</t>
+  </si>
+  <si>
+    <t>8011.21</t>
+  </si>
+  <si>
+    <t>7745.32</t>
+  </si>
+  <si>
+    <t>7745.33</t>
+  </si>
+  <si>
+    <t>7745.34</t>
+  </si>
+  <si>
+    <t>7745.35</t>
+  </si>
+  <si>
+    <t>8145.18</t>
+  </si>
+  <si>
+    <t>8145.19</t>
+  </si>
+  <si>
+    <t>8145.20</t>
+  </si>
+  <si>
+    <t>8145.21</t>
+  </si>
+  <si>
+    <t>11800.31</t>
+  </si>
+  <si>
+    <t>11800.32</t>
+  </si>
+  <si>
+    <t>11800.33</t>
+  </si>
+  <si>
+    <t>9175.36</t>
+  </si>
+  <si>
+    <t>9175.37</t>
+  </si>
+  <si>
+    <t>9175.38</t>
   </si>
 </sst>
 </file>
@@ -236,9 +386,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -524,14 +675,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -539,408 +690,408 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1">
-        <v>6800</v>
+      <c r="B2" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1">
-        <v>6800</v>
+      <c r="B3" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1">
-        <v>6800</v>
+      <c r="B4" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1">
-        <v>6800</v>
+      <c r="B5" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1">
-        <v>6800</v>
+      <c r="B6" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1">
-        <v>6800</v>
+      <c r="B7" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1">
-        <v>6800</v>
+      <c r="B8" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1">
-        <v>6800</v>
+      <c r="B9" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1">
-        <v>6800</v>
+      <c r="B10" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="1">
-        <v>6800</v>
+      <c r="B11" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="1">
-        <v>6800</v>
+      <c r="B12" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="1">
-        <v>6800</v>
+      <c r="B13" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="1">
-        <v>6800</v>
+      <c r="B14" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="1">
-        <v>6800</v>
+      <c r="B15" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="1">
-        <v>6800</v>
+      <c r="B16" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="1">
-        <v>6800</v>
+      <c r="B17" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="1">
-        <v>6800</v>
+      <c r="B18" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="1">
-        <v>6800</v>
+      <c r="B19" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="1">
-        <v>6800</v>
+      <c r="B20" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="1">
-        <v>7200</v>
+      <c r="B21" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="1">
-        <v>7200</v>
+      <c r="B22" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="1">
-        <v>7200</v>
+      <c r="B23" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="1">
-        <v>7200</v>
+      <c r="B24" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="1">
-        <v>7200</v>
+      <c r="B25" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="1">
-        <v>7200</v>
+      <c r="B26" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="1">
-        <v>6254</v>
+      <c r="B27" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="1">
-        <v>6254</v>
+      <c r="B28" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="1">
-        <v>6254</v>
+      <c r="B29" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="1">
-        <v>6254</v>
+      <c r="B30" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="1">
-        <v>6254</v>
+      <c r="B31" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="1">
-        <v>8011</v>
+      <c r="B32" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="1">
-        <v>8011</v>
+      <c r="B33" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="1">
-        <v>8011</v>
+      <c r="B34" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="1">
-        <v>8011</v>
+      <c r="B35" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="1">
-        <v>8011</v>
+      <c r="B36" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="1">
-        <v>8011</v>
+      <c r="B37" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="1">
-        <v>8011</v>
+      <c r="B38" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="1">
-        <v>7745</v>
+      <c r="B39" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="1">
-        <v>7745</v>
+      <c r="B40" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="1">
-        <v>7745</v>
+      <c r="B41" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="1">
-        <v>7745</v>
+      <c r="B42" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="1">
-        <v>8145</v>
+      <c r="B43" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="1">
-        <v>8145</v>
+      <c r="B44" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="1">
-        <v>8145</v>
+      <c r="B45" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="1">
-        <v>8145</v>
+      <c r="B46" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="1">
-        <v>11800</v>
+      <c r="B47" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="1">
-        <v>11800</v>
+      <c r="B48" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="1">
-        <v>11800</v>
+      <c r="B49" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="1">
-        <v>9175</v>
+      <c r="B50" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="1">
-        <v>9175</v>
+      <c r="B51" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="1">
-        <v>9175</v>
+      <c r="B52" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
